--- a/02_Codigo/04_BattBankDesign/01_codes/02_Pnom025/CAPEX_OPEX_ROI_25.xlsx
+++ b/02_Codigo/04_BattBankDesign/01_codes/02_Pnom025/CAPEX_OPEX_ROI_25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desar\Documents\Tesis Magister\Tesis_Msc_LSZ\02_Codigo\04_BattBankDesign\01_codes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desar\Documents\Tesis Magister\Tesis_Msc_LSZ\02_Codigo\04_BattBankDesign\01_codes\02_Pnom025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122383B0-041D-4953-B778-608026CFD18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2A4AF0-C1ED-4F17-AE71-A7ADFF3EB48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-11610" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
+    <workbookView xWindow="-28920" yWindow="-11610" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Costs 25%" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="78">
   <si>
     <t>Lowest Cost ($/kWh)</t>
   </si>
@@ -263,6 +263,18 @@
   </si>
   <si>
     <t>Cost LTO</t>
+  </si>
+  <si>
+    <t>20 años</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>10 años</t>
+  </si>
+  <si>
+    <t>15 años</t>
   </si>
 </sst>
 </file>
@@ -337,7 +349,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -357,12 +369,13 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="42" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda [0]" xfId="1" builtinId="7"/>
@@ -710,14 +723,14 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
@@ -803,14 +816,14 @@
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
@@ -855,14 +868,14 @@
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
@@ -935,14 +948,14 @@
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.35">
@@ -988,14 +1001,14 @@
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
@@ -1043,14 +1056,14 @@
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E22" t="s">
@@ -1083,14 +1096,14 @@
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E25" t="s">
@@ -1150,18 +1163,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="E3" s="15" t="s">
+      <c r="C3" s="16"/>
+      <c r="E3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="H3" s="15" t="s">
+      <c r="F3" s="16"/>
+      <c r="H3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="15"/>
+      <c r="I3" s="16"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
@@ -1422,14 +1435,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="E2" s="15" t="s">
+      <c r="C2" s="16"/>
+      <c r="E2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
@@ -1602,14 +1615,14 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C14" s="1">
         <f>50*C8*0</f>
         <v>0</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="15" t="s">
         <v>63</v>
       </c>
       <c r="F14" s="1">
@@ -1671,14 +1684,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9148CD0-5187-4E9B-AB88-218957DBEFDE}">
-  <dimension ref="B2:L13"/>
+  <dimension ref="B1:P13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="H1" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="K1" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="16"/>
+      <c r="N1" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="O1" s="16"/>
+    </row>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>44</v>
       </c>
@@ -1696,16 +1724,30 @@
         <v>48</v>
       </c>
       <c r="I2" s="8">
-        <f>SUM(C9:L9)+SUM(C13:L13)-F2</f>
-        <v>949002.82247290574</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+        <f>SUM($C$9:$L$9)-F2</f>
+        <v>-530992.48142388556</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="8">
+        <f>SUM($C$9:$L$9)+SUM($C$13:$G$13)-F2</f>
+        <v>986682.11463039368</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="8">
+        <f>SUM($C$9:$L$9)+SUM($C$13:$L$13)-F2</f>
+        <v>2019585.9432699243</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>46</v>
       </c>
       <c r="C3" s="10">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E3" t="s">
         <v>50</v>
@@ -1718,11 +1760,25 @@
         <v>52</v>
       </c>
       <c r="I3" s="8">
-        <f>SUM(C9:L9)+SUM(C13:L13)-F3</f>
-        <v>1736502.8224729057</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+        <f t="shared" ref="I3:I4" si="0">SUM($C$9:$L$9)-F3</f>
+        <v>256507.51857611444</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3" s="8">
+        <f t="shared" ref="L3:L4" si="1">SUM($C$9:$L$9)+SUM($C$13:$G$13)-F3</f>
+        <v>1774182.1146303937</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O3" s="8">
+        <f t="shared" ref="O3:O4" si="2">SUM($C$9:$L$9)+SUM($C$13:$L$13)-F3</f>
+        <v>2807085.9432699243</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>45</v>
       </c>
@@ -1741,25 +1797,42 @@
         <v>53</v>
       </c>
       <c r="I4" s="8">
-        <f>SUM(C9:L9)+SUM(C13:L13)-F4</f>
-        <v>-1570997.1775270943</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C7" s="15" t="s">
+        <f t="shared" si="0"/>
+        <v>-3050992.4814238856</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="8">
+        <f t="shared" si="1"/>
+        <v>-1533317.8853696063</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O4" s="8">
+        <f t="shared" si="2"/>
+        <v>-500414.05673007574</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C7" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="P7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C8">
         <v>1</v>
       </c>
@@ -1791,49 +1864,49 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C9" s="5">
         <f>$C$4/((1+$C$3)^C8)</f>
-        <v>746029.09090909082</v>
+        <v>759844.44444444438</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" ref="C9:L9" si="0">$C$4/((1+$C$3)^D8)</f>
-        <v>678208.26446280978</v>
+        <f t="shared" ref="D9:L9" si="3">$C$4/((1+$C$3)^D8)</f>
+        <v>703559.67078189296</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="0"/>
-        <v>616552.96769346332</v>
+        <f t="shared" si="3"/>
+        <v>651444.13961286377</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="0"/>
-        <v>560502.69790314848</v>
+        <f t="shared" si="3"/>
+        <v>603189.018160059</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="0"/>
-        <v>509547.90718468046</v>
+        <f t="shared" si="3"/>
+        <v>558508.35014820285</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="0"/>
-        <v>463225.37016789126</v>
+        <f t="shared" si="3"/>
+        <v>517137.36124833586</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>421113.97287990106</v>
+        <f t="shared" si="3"/>
+        <v>478830.89004475542</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="0"/>
-        <v>382830.88443627377</v>
+        <f t="shared" si="3"/>
+        <v>443361.93522662536</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="0"/>
-        <v>348028.0767602488</v>
+        <f t="shared" si="3"/>
+        <v>410520.31039502349</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="0"/>
-        <v>316389.16069113527</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>380111.39851391059</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C12">
         <v>11</v>
       </c>
@@ -1865,51 +1938,54 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C13" s="5">
-        <f t="shared" ref="C13:L13" si="1">$C$4/((1+$C$3)^C12)</f>
-        <v>287626.50971921382</v>
+        <f t="shared" ref="C13:L13" si="4">$C$4/((1+$C$3)^C12)</f>
+        <v>351954.99862399133</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" si="1"/>
-        <v>261478.64519928533</v>
+        <f t="shared" si="4"/>
+        <v>325884.2579851771</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="1"/>
-        <v>237707.85927207756</v>
+        <f t="shared" si="4"/>
+        <v>301744.68331960845</v>
       </c>
       <c r="F13" s="5">
-        <f t="shared" si="1"/>
-        <v>216098.05388370683</v>
+        <f t="shared" si="4"/>
+        <v>279393.22529593366</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" si="1"/>
-        <v>196452.77625791531</v>
+        <f t="shared" si="4"/>
+        <v>258697.43082956821</v>
       </c>
       <c r="H13" s="5">
-        <f t="shared" si="1"/>
-        <v>178593.43296174117</v>
+        <f t="shared" si="4"/>
+        <v>239534.65817552613</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="1"/>
-        <v>162357.66632885562</v>
+        <f t="shared" si="4"/>
+        <v>221791.35016252418</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="1"/>
-        <v>147597.87848077781</v>
+        <f t="shared" si="4"/>
+        <v>205362.36126159644</v>
       </c>
       <c r="K13" s="5">
-        <f t="shared" si="1"/>
-        <v>134179.8895279798</v>
+        <f t="shared" si="4"/>
+        <v>190150.33450147818</v>
       </c>
       <c r="L13" s="5">
-        <f t="shared" si="1"/>
-        <v>121981.71775270892</v>
+        <f t="shared" si="4"/>
+        <v>176065.12453840574</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="C7:L7"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:O1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1918,13 +1994,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8641AB-FA05-4689-970F-41940E5E4D56}">
-  <dimension ref="B2:V19"/>
+  <dimension ref="B1:V19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="E1" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="17"/>
+      <c r="H1" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="17"/>
+      <c r="K1" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="17"/>
+    </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>45</v>
@@ -1937,6 +2027,20 @@
         <v>54</v>
       </c>
       <c r="F2" s="11">
+        <f>IRR(B9:L9)</f>
+        <v>6.0084698435833195E-2</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="11">
+        <f>IRR(B9:Q9)</f>
+        <v>0.10588754031996528</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="11">
         <f>IRR(B9:V9)</f>
         <v>0.12242942493009346</v>
       </c>
@@ -1947,6 +2051,20 @@
         <v>58</v>
       </c>
       <c r="F3" s="11">
+        <f>IRR(B14:L14)</f>
+        <v>9.0715047244378288E-2</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="11">
+        <f>IRR(B14:Q14)</f>
+        <v>0.13195928106765797</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="11">
         <f>IRR(B14:V14)</f>
         <v>0.14608635113200341</v>
       </c>
@@ -1956,23 +2074,37 @@
         <v>59</v>
       </c>
       <c r="F4" s="11">
+        <f>IRR(B19:L19)</f>
+        <v>-7.547152523541989E-3</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="11">
+        <f>IRR(B19:Q19)</f>
+        <v>4.9314243098562693E-2</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="11">
         <f>IRR(B19:V19)</f>
         <v>7.2041989418216046E-2</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B8">
@@ -2126,18 +2258,18 @@
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B13">
@@ -2291,18 +2423,18 @@
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B18">
@@ -2379,7 +2511,7 @@
         <v>820632</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" ref="C19:V19" si="2">$C$2</f>
+        <f t="shared" ref="D19:V19" si="2">$C$2</f>
         <v>820632</v>
       </c>
       <c r="E19" s="5">
@@ -2456,10 +2588,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="C7:L7"/>
     <mergeCell ref="C12:L12"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2518,7 +2653,7 @@
         <v>61</v>
       </c>
       <c r="I3" s="12">
-        <f t="shared" ref="I3:I4" si="0">F3/$C$4</f>
+        <f t="shared" ref="I3" si="0">F3/$C$4</f>
         <v>6.3975082619249557</v>
       </c>
     </row>
@@ -2546,18 +2681,18 @@
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8">
@@ -2584,7 +2719,7 @@
       <c r="I8">
         <v>7</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8">
         <v>8</v>
       </c>
       <c r="K8">
@@ -2627,7 +2762,7 @@
         <f t="shared" si="1"/>
         <v>-2042319.7287990148</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="5">
         <f t="shared" si="1"/>
         <v>-1659488.8443627411</v>
       </c>
@@ -2715,18 +2850,18 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17">
@@ -2750,7 +2885,7 @@
       <c r="H17">
         <v>6</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17">
         <v>7</v>
       </c>
       <c r="J17">
@@ -2792,7 +2927,7 @@
         <f t="shared" si="3"/>
         <v>-1675933.7016789156</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="5">
         <f t="shared" si="3"/>
         <v>-1254819.7287990146</v>
       </c>
@@ -2884,18 +3019,18 @@
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27">
@@ -2982,7 +3117,7 @@
       <c r="C31">
         <v>11</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31">
         <v>12</v>
       </c>
       <c r="E31">
@@ -3015,7 +3150,7 @@
         <f>$C$4/((1+$C$3)^C31)+L28</f>
         <v>-3227445.0971921436</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="5">
         <f t="shared" ref="D32:L32" si="6">$C$4/((1+$C$3)^D31)+C32</f>
         <v>-2965966.4519928582</v>
       </c>

--- a/02_Codigo/04_BattBankDesign/01_codes/02_Pnom025/CAPEX_OPEX_ROI_25.xlsx
+++ b/02_Codigo/04_BattBankDesign/01_codes/02_Pnom025/CAPEX_OPEX_ROI_25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desar\Documents\Tesis Magister\Tesis_Msc_LSZ\02_Codigo\04_BattBankDesign\01_codes\02_Pnom025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell PC\Desktop\Tesis Magister\02_Codigo\04_BattBankDesign\01_codes\02_Pnom025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2A4AF0-C1ED-4F17-AE71-A7ADFF3EB48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D32AA41-D265-44C1-8249-82A8F66CE0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-11610" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Costs 25%" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="84">
   <si>
     <t>Lowest Cost ($/kWh)</t>
   </si>
@@ -136,18 +136,6 @@
     <t>Conventional Tug</t>
   </si>
   <si>
-    <t>Lowest yearly fuel consumption (L)</t>
-  </si>
-  <si>
-    <t>Highest yearly fuel consumption (L)</t>
-  </si>
-  <si>
-    <t>Average yearly fuel consumption (L)</t>
-  </si>
-  <si>
-    <t>Hybrid Tug</t>
-  </si>
-  <si>
     <t>Fuel Cost ($/L)</t>
   </si>
   <si>
@@ -178,9 +166,6 @@
     <t>Lifespan</t>
   </si>
   <si>
-    <t>Yearly Profit ($)</t>
-  </si>
-  <si>
     <t>Discount Rate (%)</t>
   </si>
   <si>
@@ -247,15 +232,6 @@
     <t>Percentage of the cost subsidized by the government</t>
   </si>
   <si>
-    <t>Lowest yearly CO2 emissions generated (t)</t>
-  </si>
-  <si>
-    <t>Highest yearly CO2 emissions generated (t)</t>
-  </si>
-  <si>
-    <t>Average yearly CO2 emissions generated (t)</t>
-  </si>
-  <si>
     <t>Cost NMC</t>
   </si>
   <si>
@@ -275,15 +251,58 @@
   </si>
   <si>
     <t>15 años</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Battery Maintenance</t>
+  </si>
+  <si>
+    <t>Lowest annual fuel consumption (L)</t>
+  </si>
+  <si>
+    <t>Highest annual fuel consumption (L)</t>
+  </si>
+  <si>
+    <t>Average annual fuel consumption (L)</t>
+  </si>
+  <si>
+    <t>Lowest annual CO2 emissions generated (t)</t>
+  </si>
+  <si>
+    <t>Highest annual CO2 emissions generated (t)</t>
+  </si>
+  <si>
+    <t>Average annual CO2 emissions generated (t)</t>
+  </si>
+  <si>
+    <t>Hybrid Tug - NMC</t>
+  </si>
+  <si>
+    <t>Hybrid Tug - LFP</t>
+  </si>
+  <si>
+    <t>Hybrid Tug - LTO</t>
+  </si>
+  <si>
+    <t>Annual Profit NMC ($)</t>
+  </si>
+  <si>
+    <t>Annual Profit LFP ($)</t>
+  </si>
+  <si>
+    <t>Annual Profit LTO ($)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="42" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0.0_ ;_ &quot;$&quot;* \-#,##0.0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;* #,##0.0_ ;_ &quot;$&quot;* \-#,##0.0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -346,28 +365,28 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -376,6 +395,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda [0]" xfId="1" builtinId="7"/>
@@ -713,16 +738,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CC14D7A-AB81-456B-B0DB-733EF237E819}">
   <dimension ref="B3:H26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
         <v>2</v>
       </c>
@@ -732,7 +757,7 @@
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>7</v>
       </c>
@@ -749,7 +774,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -757,21 +782,21 @@
         <v>6300</v>
       </c>
       <c r="D5">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="E5">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="F5">
         <f>(D5+E5)/2</f>
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="G5" s="4">
         <f>F5*C5</f>
-        <v>4095000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+        <v>5040000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -779,21 +804,21 @@
         <v>6300</v>
       </c>
       <c r="D6">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="E6">
         <v>600</v>
       </c>
       <c r="F6">
         <f t="shared" ref="F6:F7" si="0">(D6+E6)/2</f>
-        <v>525</v>
+        <v>450</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" ref="G6:G7" si="1">F6*C6</f>
-        <v>3307500</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+        <v>2835000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -801,21 +826,21 @@
         <v>6300</v>
       </c>
       <c r="D7">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E7">
         <v>1200</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="1"/>
-        <v>6615000</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+        <v>6300000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="16" t="s">
         <v>9</v>
       </c>
@@ -825,7 +850,7 @@
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -845,7 +870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>4</v>
       </c>
@@ -856,18 +881,18 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="F10">
         <f>(D10+E10)/2</f>
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="G10" s="4">
         <f>B10*C10*F10</f>
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
         <v>12</v>
       </c>
@@ -877,7 +902,7 @@
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>10</v>
       </c>
@@ -897,7 +922,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -908,21 +933,21 @@
         <v>500</v>
       </c>
       <c r="E13">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="F13">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="G13">
         <f>(E13+F13)/2</f>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="H13" s="4">
         <f>C13*D13*G13</f>
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>14</v>
       </c>
@@ -936,18 +961,18 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="G14">
         <f>(E14+F14)/2</f>
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="H14" s="4">
         <f>C14*D14*G14</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="16" t="s">
         <v>15</v>
       </c>
@@ -958,7 +983,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>10</v>
       </c>
@@ -978,7 +1003,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C17">
         <v>1</v>
       </c>
@@ -1000,7 +1025,7 @@
         <v>825000</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
         <v>16</v>
       </c>
@@ -1010,7 +1035,7 @@
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>10</v>
       </c>
@@ -1030,7 +1055,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -1055,7 +1080,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="16" t="s">
         <v>20</v>
       </c>
@@ -1065,7 +1090,7 @@
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E22" t="s">
         <v>22</v>
       </c>
@@ -1079,7 +1104,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E23" s="1">
         <v>100000</v>
       </c>
@@ -1095,7 +1120,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="16" t="s">
         <v>21</v>
       </c>
@@ -1105,7 +1130,7 @@
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
         <v>22</v>
       </c>
@@ -1119,7 +1144,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E26" s="1">
         <v>50000</v>
       </c>
@@ -1152,17 +1177,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29A8CAA-C5C8-4FF3-BA68-5F71D3D769DB}">
   <dimension ref="B3:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="43.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
         <v>3</v>
       </c>
@@ -1176,76 +1201,76 @@
       </c>
       <c r="I3" s="16"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="5">
         <f>'Costs 25%'!G5</f>
-        <v>4095000</v>
+        <v>5040000</v>
       </c>
       <c r="E4" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="5">
         <f>'Costs 25%'!G6</f>
-        <v>3307500</v>
+        <v>2835000</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
       </c>
       <c r="I4" s="5">
         <f>'Costs 25%'!G7</f>
-        <v>6615000</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+        <v>6300000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="5">
         <f>'Costs 25%'!$G$10</f>
-        <v>125000</v>
+        <v>250000</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="5">
         <f>'Costs 25%'!$G$10</f>
-        <v>125000</v>
+        <v>250000</v>
       </c>
       <c r="H5" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="5">
         <f>'Costs 25%'!$G$10</f>
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="5">
         <f>'Costs 25%'!$H$13+'Costs 25%'!$H$14</f>
-        <v>450000</v>
+        <v>720000</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="5">
         <f>'Costs 25%'!$H$13+'Costs 25%'!$H$14</f>
-        <v>450000</v>
+        <v>720000</v>
       </c>
       <c r="H6" t="s">
         <v>27</v>
       </c>
       <c r="I6" s="5">
         <f>'Costs 25%'!$H$13+'Costs 25%'!$H$14</f>
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+        <v>720000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>15</v>
       </c>
@@ -1268,7 +1293,7 @@
         <v>825000</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -1291,7 +1316,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>28</v>
       </c>
@@ -1314,7 +1339,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>29</v>
       </c>
@@ -1337,78 +1362,101 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C11" s="8">
         <f>SUM(C4:C10)</f>
-        <v>6037500</v>
+        <v>7377500</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F11" s="8">
         <f>SUM(F4:F10)</f>
-        <v>5250000</v>
+        <v>5172500</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I11" s="8">
         <f>SUM(I4:I10)</f>
-        <v>8557500</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B12" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="1">
+        <v>8637500</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="18">
+        <f>C11*0.035</f>
+        <v>258212.50000000003</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="18">
+        <f>F11*0.035</f>
+        <v>181037.50000000003</v>
+      </c>
+      <c r="H12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" s="18">
+        <f>I11*0.035</f>
+        <v>302312.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="1">
         <f>C11*C17</f>
         <v>0</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="E13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="1">
         <f>F11*C17</f>
         <v>0</v>
       </c>
-      <c r="H12" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="H13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="1">
         <f>I11*C17</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="8">
-        <f>C11-C12</f>
-        <v>6037500</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="8">
-        <f>F11-F12</f>
-        <v>5250000</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="8">
-        <f>I11-I12</f>
-        <v>8557500</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="8">
+        <f>C11-C13+C12</f>
+        <v>7635712.5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="8">
+        <f>F11-F13+F12</f>
+        <v>5353537.5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="8">
+        <f>I11-I13+I12</f>
+        <v>8939812.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C17" s="10">
         <v>0</v>
@@ -1426,257 +1474,487 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAAF4CD5-5B27-45B4-BE42-4FE58799A9A6}">
-  <dimension ref="B2:F19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:L19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C2" s="16"/>
       <c r="E2" s="16" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="F2" s="16"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H2" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="16"/>
+      <c r="K2" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="16"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C3" s="6">
         <f>5366*365</f>
         <v>1958590</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F3" s="6">
         <f>1929*365</f>
         <v>704085</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="6">
+        <f>1929*365</f>
+        <v>704085</v>
+      </c>
+      <c r="K3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="6">
+        <f>1929*365</f>
+        <v>704085</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C4" s="6">
         <f>6385*365</f>
         <v>2330525</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F4" s="6">
         <f>4030*365</f>
         <v>1470950</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="6">
+        <f>4030*365</f>
+        <v>1470950</v>
+      </c>
+      <c r="K4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L4" s="6">
+        <f>4030*365</f>
+        <v>1470950</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="C5" s="6">
         <f>(C3+C4)/2</f>
         <v>2144557.5</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="F5">
         <f>(F3+F4)/2</f>
         <v>1087517.5</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5">
+        <f>(I3+I4)/2</f>
+        <v>1087517.5</v>
+      </c>
+      <c r="K5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5">
+        <f>(L3+L4)/2</f>
+        <v>1087517.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C6">
         <f>14.3*365</f>
         <v>5219.5</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F6">
         <f>5.1*365</f>
         <v>1861.4999999999998</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6">
+        <f>5.1*365</f>
+        <v>1861.4999999999998</v>
+      </c>
+      <c r="K6" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6">
+        <f>5.1*365</f>
+        <v>1861.4999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C7">
         <f>17*365</f>
         <v>6205</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F7">
         <f>10.8*365</f>
         <v>3942.0000000000005</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7">
+        <f>10.8*365</f>
+        <v>3942.0000000000005</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7">
+        <f>10.8*365</f>
+        <v>3942.0000000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C8">
         <f>(C6+C7)/2</f>
         <v>5712.25</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F8">
         <f>(F6+F7)/2</f>
         <v>2901.75</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8">
+        <f>(I6+I7)/2</f>
+        <v>2901.75</v>
+      </c>
+      <c r="K8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8">
+        <f>(L6+L7)/2</f>
+        <v>2901.75</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C9" s="7">
         <f>0.8</f>
         <v>0.8</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F9" s="7">
         <f>0.8</f>
         <v>0.8</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="7">
+        <f>0.8</f>
+        <v>0.8</v>
+      </c>
+      <c r="K9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="7">
+        <f>0.8</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C10" s="4">
         <f>C5*C9</f>
         <v>1715646</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F10" s="4">
         <f>F5*F9</f>
         <v>870014</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="4">
+        <f>I5*I9</f>
+        <v>870014</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="4">
+        <f>L5*L9</f>
+        <v>870014</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1">
         <v>30000</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="1">
+        <v>30000</v>
+      </c>
+      <c r="K11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1">
         <v>40000</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F12" s="1">
         <v>20000</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="1">
+        <v>20000</v>
+      </c>
+      <c r="K12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F13" s="1">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+        <f>'Costs 25%'!G5/15</f>
+        <v>336000</v>
+      </c>
+      <c r="H13" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="1">
+        <f>'Costs 25%'!G6/15</f>
+        <v>189000</v>
+      </c>
+      <c r="K13" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1">
         <f>50*C8*0</f>
         <v>0</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F14" s="1">
         <f>50*F8*0</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H14" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="1">
+        <f>50*I8*0</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="1">
+        <f>50*L8*0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C15" s="9">
         <f>SUM(C10:C14)</f>
         <v>1755646</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F15" s="9">
         <f>SUM(F10:F14)</f>
-        <v>935014</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="5">
+        <v>1256014</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="9">
+        <f>SUM(I10:I14)</f>
+        <v>1109014</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="9">
+        <f>SUM(L10:L14)</f>
+        <v>920014</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="5">
         <f>C15</f>
         <v>1755646</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="5">
+      <c r="H17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="5">
+        <f>C15</f>
+        <v>1755646</v>
+      </c>
+      <c r="K17" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" s="5">
+        <f>C15</f>
+        <v>1755646</v>
+      </c>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="5">
         <f>F15</f>
-        <v>935014</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="8">
-        <f>C17-C18</f>
-        <v>820632</v>
+        <v>1256014</v>
+      </c>
+      <c r="H18" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="5">
+        <f>I15</f>
+        <v>1109014</v>
+      </c>
+      <c r="K18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="5">
+        <f>L15</f>
+        <v>920014</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="8">
+        <f>F17-F18</f>
+        <v>499632</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="8">
+        <f>I17-I18</f>
+        <v>646632</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19" s="8">
+        <f>L17-L18</f>
+        <v>835632</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1684,140 +1962,159 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9148CD0-5187-4E9B-AB88-218957DBEFDE}">
-  <dimension ref="B1:P13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:P16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="H1" s="16" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I1" s="16"/>
       <c r="K1" s="16" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L1" s="16"/>
       <c r="N1" s="16" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O1" s="16"/>
     </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F2" s="5">
-        <f>'CAPEX 25%'!C13</f>
-        <v>6037500</v>
+        <f>'CAPEX 25%'!C14</f>
+        <v>7635712.5</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I2" s="8">
         <f>SUM($C$9:$L$9)-F2</f>
-        <v>-530992.48142388556</v>
+        <v>-4283141.1104840897</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L2" s="8">
-        <f>SUM($C$9:$L$9)+SUM($C$13:$G$13)-F2</f>
-        <v>986682.11463039368</v>
+        <f>SUM($C$9:$L$9)+SUM($C$14:$G$14)-F2</f>
+        <v>-3359123.0441939728</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="O2" s="8">
-        <f>SUM($C$9:$L$9)+SUM($C$13:$L$13)-F2</f>
-        <v>2019585.9432699243</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
+        <f>SUM($C$9:$L$9)+SUM($C$14:$L$14)-F2</f>
+        <v>-2730251.8745212983</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C3" s="10">
         <v>0.08</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F3" s="5">
-        <f>'CAPEX 25%'!F13</f>
-        <v>5250000</v>
+        <f>'CAPEX 25%'!F14</f>
+        <v>5353537.5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I3" s="8">
-        <f t="shared" ref="I3:I4" si="0">SUM($C$9:$L$9)-F3</f>
-        <v>256507.51857611444</v>
+        <f>SUM($C$10:$L$10)-F3</f>
+        <v>-1014584.1448396975</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="L3" s="8">
-        <f t="shared" ref="L3:L4" si="1">SUM($C$9:$L$9)+SUM($C$13:$G$13)-F3</f>
-        <v>1774182.1146303937</v>
+        <f>SUM($C$10:$L$10)+SUM($C$15:$G$15)-F3</f>
+        <v>181295.32293120399</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="O3" s="8">
-        <f t="shared" ref="O3:O4" si="2">SUM($C$9:$L$9)+SUM($C$13:$L$13)-F3</f>
-        <v>2807085.9432699243</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
+        <f>SUM($C$10:$L$10)+SUM($C$15:$L$15)-F3</f>
+        <v>995190.79437374696</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C4" s="5">
-        <f>'OPEX 25%'!C19</f>
-        <v>820632</v>
+        <f>'OPEX 25%'!F19</f>
+        <v>499632</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F4" s="5">
-        <f>'CAPEX 25%'!I13</f>
-        <v>8557500</v>
+        <f>'CAPEX 25%'!I14</f>
+        <v>8939812.5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I4" s="8">
-        <f t="shared" si="0"/>
-        <v>-3050992.4814238856</v>
+        <f>SUM($C$11:$L$11)-F4</f>
+        <v>-2766443.6718342882</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="L4" s="8">
-        <f t="shared" si="1"/>
-        <v>-1533317.8853696063</v>
+        <f>SUM($C$11:$L$11)+SUM($C$16:$G$16)-F4</f>
+        <v>-1064972.274406109</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O4" s="8">
-        <f t="shared" si="2"/>
-        <v>-500414.05673007574</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+        <f>SUM($C$11:$L$11)+SUM($C$16:$L$16)-F4</f>
+        <v>93020.568917047232</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="5">
+        <f>'OPEX 25%'!I19</f>
+        <v>646632</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="5">
+        <f>'OPEX 25%'!L15</f>
+        <v>920014</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C7" s="16" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -1829,155 +2126,345 @@
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
       <c r="P7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C8" s="2">
         <v>1</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>2</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>3</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>4</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>5</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>6</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>8</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>9</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9" s="19" t="s">
+        <v>3</v>
+      </c>
       <c r="C9" s="5">
         <f>$C$4/((1+$C$3)^C8)</f>
-        <v>759844.44444444438</v>
+        <v>462622.22222222219</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" ref="D9:L9" si="3">$C$4/((1+$C$3)^D8)</f>
-        <v>703559.67078189296</v>
+        <f t="shared" ref="D9:L9" si="0">$C$4/((1+$C$3)^D8)</f>
+        <v>428353.90946502052</v>
       </c>
       <c r="E9" s="5">
+        <f t="shared" si="0"/>
+        <v>396623.99024538934</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>367244.43541239755</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="0"/>
+        <v>340041.14390036807</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="0"/>
+        <v>314852.9110188593</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>291530.47316561046</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="0"/>
+        <v>269935.62330149114</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="0"/>
+        <v>249940.39194582513</v>
+      </c>
+      <c r="L9" s="5">
+        <f t="shared" si="0"/>
+        <v>231426.28883872696</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5">
+        <f>$C$5/((1+$C$3)^C8)</f>
+        <v>598733.33333333326</v>
+      </c>
+      <c r="D10" s="5">
+        <f>$C$5/((1+$C$3)^D8)</f>
+        <v>554382.7160493827</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" ref="D10:L10" si="1">$C$5/((1+$C$3)^E8)</f>
+        <v>513317.3296753543</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="1"/>
+        <v>475293.82377347618</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="1"/>
+        <v>440086.87386432977</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" si="1"/>
+        <v>407487.84617067565</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="1"/>
+        <v>377303.56126914412</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="1"/>
+        <v>349355.1493232816</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="1"/>
+        <v>323476.99011414958</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" si="1"/>
+        <v>299515.73158717557</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B11" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5">
+        <f>$C$6/((1+$C$3)^C8)</f>
+        <v>851864.81481481472</v>
+      </c>
+      <c r="D11" s="5">
+        <f t="shared" ref="D11:L11" si="2">$C$6/((1+$C$3)^D8)</f>
+        <v>788763.71742112481</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" si="2"/>
+        <v>730336.77538993035</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="2"/>
+        <v>676237.75499067619</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" si="2"/>
+        <v>626146.06943581125</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="2"/>
+        <v>579764.87910723255</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="2"/>
+        <v>536819.33250669681</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="2"/>
+        <v>497054.93750620075</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="2"/>
+        <v>460236.0532464821</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="2"/>
+        <v>426144.49374674272</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B12" s="19"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B13" s="19"/>
+      <c r="C13" s="2">
+        <v>11</v>
+      </c>
+      <c r="D13" s="2">
+        <v>12</v>
+      </c>
+      <c r="E13" s="2">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2">
+        <v>14</v>
+      </c>
+      <c r="G13" s="2">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2">
+        <v>16</v>
+      </c>
+      <c r="I13" s="2">
+        <v>17</v>
+      </c>
+      <c r="J13" s="2">
+        <v>18</v>
+      </c>
+      <c r="K13" s="2">
+        <v>19</v>
+      </c>
+      <c r="L13" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="5">
+        <f t="shared" ref="C14:L14" si="3">$C$4/((1+$C$3)^C13)</f>
+        <v>214283.60077659905</v>
+      </c>
+      <c r="D14" s="5">
         <f t="shared" si="3"/>
-        <v>651444.13961286377</v>
-      </c>
-      <c r="F9" s="5">
+        <v>198410.7414598139</v>
+      </c>
+      <c r="E14" s="5">
         <f t="shared" si="3"/>
-        <v>603189.018160059</v>
-      </c>
-      <c r="G9" s="5">
+        <v>183713.6494998277</v>
+      </c>
+      <c r="F14" s="5">
         <f t="shared" si="3"/>
-        <v>558508.35014820285</v>
-      </c>
-      <c r="H9" s="5">
+        <v>170105.23101835896</v>
+      </c>
+      <c r="G14" s="5">
         <f t="shared" si="3"/>
-        <v>517137.36124833586</v>
-      </c>
-      <c r="I9" s="5">
+        <v>157504.84353551752</v>
+      </c>
+      <c r="H14" s="5">
         <f t="shared" si="3"/>
-        <v>478830.89004475542</v>
-      </c>
-      <c r="J9" s="5">
+        <v>145837.81808844217</v>
+      </c>
+      <c r="I14" s="5">
         <f t="shared" si="3"/>
-        <v>443361.93522662536</v>
-      </c>
-      <c r="K9" s="5">
+        <v>135035.01674855757</v>
+      </c>
+      <c r="J14" s="5">
         <f t="shared" si="3"/>
-        <v>410520.31039502349</v>
-      </c>
-      <c r="L9" s="5">
+        <v>125032.42291533106</v>
+      </c>
+      <c r="K14" s="5">
         <f t="shared" si="3"/>
-        <v>380111.39851391059</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C12">
-        <v>11</v>
-      </c>
-      <c r="D12">
-        <v>12</v>
-      </c>
-      <c r="E12">
-        <v>13</v>
-      </c>
-      <c r="F12">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>15</v>
-      </c>
-      <c r="H12">
-        <v>16</v>
-      </c>
-      <c r="I12">
-        <v>17</v>
-      </c>
-      <c r="J12">
-        <v>18</v>
-      </c>
-      <c r="K12">
-        <v>19</v>
-      </c>
-      <c r="L12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C13" s="5">
-        <f t="shared" ref="C13:L13" si="4">$C$4/((1+$C$3)^C12)</f>
-        <v>351954.99862399133</v>
-      </c>
-      <c r="D13" s="5">
+        <v>115770.76195863985</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="3"/>
+        <v>107195.14996170357</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5">
+        <f>$C$5/((1+$C$3)^C13)</f>
+        <v>277329.38109923661</v>
+      </c>
+      <c r="D15" s="5">
+        <f t="shared" ref="D15:L15" si="4">$C$5/((1+$C$3)^D13)</f>
+        <v>256786.46398077463</v>
+      </c>
+      <c r="E15" s="5">
         <f t="shared" si="4"/>
-        <v>325884.2579851771</v>
-      </c>
-      <c r="E13" s="5">
+        <v>237765.24442664318</v>
+      </c>
+      <c r="F15" s="5">
         <f t="shared" si="4"/>
-        <v>301744.68331960845</v>
-      </c>
-      <c r="F13" s="5">
+        <v>220153.00409874364</v>
+      </c>
+      <c r="G15" s="5">
         <f t="shared" si="4"/>
-        <v>279393.22529593366</v>
-      </c>
-      <c r="G13" s="5">
+        <v>203845.37416550337</v>
+      </c>
+      <c r="H15" s="5">
+        <f>$C$5/((1+$C$3)^H13)</f>
+        <v>188745.71681991051</v>
+      </c>
+      <c r="I15" s="5">
         <f t="shared" si="4"/>
-        <v>258697.43082956821</v>
-      </c>
-      <c r="H13" s="5">
+        <v>174764.55261102825</v>
+      </c>
+      <c r="J15" s="5">
         <f t="shared" si="4"/>
-        <v>239534.65817552613</v>
-      </c>
-      <c r="I13" s="5">
+        <v>161819.03019539651</v>
+      </c>
+      <c r="K15" s="5">
         <f t="shared" si="4"/>
-        <v>221791.35016252418</v>
-      </c>
-      <c r="J13" s="5">
+        <v>149832.43536610788</v>
+      </c>
+      <c r="L15" s="5">
         <f t="shared" si="4"/>
-        <v>205362.36126159644</v>
-      </c>
-      <c r="K13" s="5">
-        <f t="shared" si="4"/>
-        <v>190150.33450147818</v>
-      </c>
-      <c r="L13" s="5">
-        <f t="shared" si="4"/>
-        <v>176065.12453840574</v>
+        <v>138733.73645009988</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B16" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5">
+        <f>$C$6/((1+$C$3)^C13)</f>
+        <v>394578.23495068768</v>
+      </c>
+      <c r="D16" s="5">
+        <f t="shared" ref="D16:L16" si="5">$C$6/((1+$C$3)^D13)</f>
+        <v>365350.21754693304</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="5"/>
+        <v>338287.2384693824</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="5"/>
+        <v>313228.92450868734</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="5"/>
+        <v>290026.78195248829</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="5"/>
+        <v>268543.31662267435</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="5"/>
+        <v>248651.21909506884</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="5"/>
+        <v>230232.61027321185</v>
+      </c>
+      <c r="K16" s="5">
+        <f t="shared" si="5"/>
+        <v>213178.34284556651</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="5"/>
+        <v>197387.35448663568</v>
       </c>
     </row>
   </sheetData>
@@ -1995,106 +2482,119 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8641AB-FA05-4689-970F-41940E5E4D56}">
   <dimension ref="B1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:22" x14ac:dyDescent="0.25">
       <c r="E1" s="17" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F1" s="17"/>
       <c r="H1" s="17" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I1" s="17"/>
       <c r="K1" s="17" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="L1" s="17"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C2" s="5">
-        <f>'OPEX 25%'!C19</f>
-        <v>820632</v>
+        <f>'OPEX 25%'!F19</f>
+        <v>499632</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F2" s="11">
         <f>IRR(B9:L9)</f>
-        <v>6.0084698435833195E-2</v>
+        <v>-7.0513545927848531E-2</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I2" s="11">
         <f>IRR(B9:Q9)</f>
-        <v>0.10588754031996528</v>
+        <v>-2.3246625458969161E-3</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L2" s="11">
         <f>IRR(B9:V9)</f>
-        <v>0.12242942493009346</v>
-      </c>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="C3" s="10"/>
+        <v>2.7111577966266731E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="5">
+        <f>'OPEX 25%'!I19</f>
+        <v>646632</v>
+      </c>
       <c r="E3" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F3" s="11">
         <f>IRR(B14:L14)</f>
-        <v>9.0715047244378288E-2</v>
+        <v>3.5897502017308236E-2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I3" s="11">
         <f>IRR(B14:Q14)</f>
-        <v>0.13195928106765797</v>
+        <v>8.5505172945715024E-2</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L3" s="11">
         <f>IRR(B14:V14)</f>
-        <v>0.14608635113200341</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.35">
+        <v>0.10412762263493414</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="5">
+        <f>'OPEX 25%'!L19</f>
+        <v>835632</v>
+      </c>
       <c r="E4" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F4" s="11">
         <f>IRR(B19:L19)</f>
-        <v>-7.547152523541989E-3</v>
+        <v>-1.2087531518178762E-2</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I4" s="11">
         <f>IRR(B19:Q19)</f>
-        <v>4.9314243098562693E-2</v>
+        <v>4.5560717055539657E-2</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="L4" s="11">
         <f>IRR(B19:V19)</f>
-        <v>7.2041989418216046E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
+        <v>6.8743520278883308E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C7" s="16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -2106,7 +2606,7 @@
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>0</v>
       </c>
@@ -2171,95 +2671,95 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
-        <f>-'CAPEX 25%'!C13</f>
-        <v>-6037500</v>
+        <f>-'CAPEX 25%'!C14</f>
+        <v>-7635712.5</v>
       </c>
       <c r="C9" s="5">
+        <f>$C$2</f>
+        <v>499632</v>
+      </c>
+      <c r="D9" s="5">
         <f t="shared" ref="C9:V9" si="0">$C$2</f>
-        <v>820632</v>
-      </c>
-      <c r="D9" s="5">
-        <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="M9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="P9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
+        <v>499632</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>820632</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.35">
+        <v>499632</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C12" s="16" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
@@ -2271,7 +2771,7 @@
       <c r="K12" s="16"/>
       <c r="L12" s="16"/>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>0</v>
       </c>
@@ -2336,95 +2836,95 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
-        <f>-'CAPEX 25%'!F13</f>
-        <v>-5250000</v>
+        <f>-'CAPEX 25%'!F14</f>
+        <v>-5353537.5</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" ref="C14:V14" si="1">$C$2</f>
-        <v>820632</v>
+        <f>$C$3</f>
+        <v>646632</v>
       </c>
       <c r="D14" s="5">
-        <f t="shared" si="1"/>
-        <v>820632</v>
+        <f t="shared" ref="D14:V14" si="1">$C$3</f>
+        <v>646632</v>
       </c>
       <c r="E14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="K14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="M14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="N14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="O14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="P14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="S14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="T14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
+        <v>646632</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="1"/>
-        <v>820632</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.35">
+        <v>646632</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C17" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
@@ -2436,7 +2936,7 @@
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>0</v>
       </c>
@@ -2501,90 +3001,90 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B19" s="5">
-        <f>-'CAPEX 25%'!I13</f>
-        <v>-8557500</v>
+        <f>-'CAPEX 25%'!I14</f>
+        <v>-8939812.5</v>
       </c>
       <c r="C19" s="5">
-        <f>$C$2</f>
-        <v>820632</v>
+        <f>$C$4</f>
+        <v>835632</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" ref="D19:V19" si="2">$C$2</f>
-        <v>820632</v>
+        <f t="shared" ref="D19:V19" si="2">$C$4</f>
+        <v>835632</v>
       </c>
       <c r="E19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="F19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="H19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="J19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="K19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="M19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="N19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="P19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="R19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="S19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="T19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="2"/>
-        <v>820632</v>
+        <v>835632</v>
       </c>
     </row>
   </sheetData>
@@ -2603,86 +3103,105 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8AEBD9-4AB4-44E4-A602-35786004721C}">
   <dimension ref="B2:L32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.1796875" customWidth="1"/>
-    <col min="12" max="12" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F2" s="5">
         <f>'CAPEX 25%'!C11</f>
-        <v>6037500</v>
+        <v>7377500</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I2" s="12">
         <f>F2/$C$4</f>
-        <v>7.3571345012136984</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+        <v>14.765867678611459</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C3" s="10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F3" s="5">
         <f>'CAPEX 25%'!F11</f>
-        <v>5250000</v>
+        <v>5172500</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I3" s="12">
-        <f t="shared" ref="I3" si="0">F3/$C$4</f>
-        <v>6.3975082619249557</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+        <f>F3/$C$5</f>
+        <v>7.9991401600910566</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C4" s="5">
-        <f>'OPEX 25%'!C19</f>
-        <v>820632</v>
+        <f>'OPEX 25%'!F19</f>
+        <v>499632</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F4" s="5">
         <f>'CAPEX 25%'!I11</f>
-        <v>8557500</v>
+        <v>8637500</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I4" s="12">
-        <f>F4/$C$4</f>
-        <v>10.427938466937677</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+        <f>F4/$C$6</f>
+        <v>10.336487831964309</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="5">
+        <f>'OPEX 25%'!I19</f>
+        <v>646632</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="5">
+        <f>'OPEX 25%'!L19</f>
+        <v>835632</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C7" s="16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -2694,7 +3213,7 @@
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>0</v>
       </c>
@@ -2719,7 +3238,7 @@
       <c r="I8">
         <v>7</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="20">
         <v>8</v>
       </c>
       <c r="K8">
@@ -2729,53 +3248,53 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <f>-F2</f>
-        <v>-6037500</v>
+        <v>-7377500</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" ref="C9:L9" si="1">$C$4/((1+$C$3)^C8)+B9</f>
-        <v>-5291470.9090909092</v>
+        <f>$C$4/((1+$C$3)^C8)+B9</f>
+        <v>-6877868</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="1"/>
-        <v>-4613262.6446280992</v>
+        <f t="shared" ref="C9:L9" si="0">$C$4/((1+$C$3)^D8)+C9</f>
+        <v>-6378236</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="1"/>
-        <v>-3996709.6769346357</v>
+        <f t="shared" si="0"/>
+        <v>-5878604</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="1"/>
-        <v>-3436206.9790314874</v>
+        <f t="shared" si="0"/>
+        <v>-5378972</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="1"/>
-        <v>-2926659.0718468069</v>
+        <f t="shared" si="0"/>
+        <v>-4879340</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="1"/>
-        <v>-2463433.7016789159</v>
+        <f t="shared" si="0"/>
+        <v>-4379708</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="1"/>
-        <v>-2042319.7287990148</v>
-      </c>
-      <c r="J9" s="5">
-        <f t="shared" si="1"/>
-        <v>-1659488.8443627411</v>
+        <f t="shared" si="0"/>
+        <v>-3880076</v>
+      </c>
+      <c r="J9" s="21">
+        <f t="shared" si="0"/>
+        <v>-3380444</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="1"/>
-        <v>-1311460.7676024924</v>
+        <f t="shared" si="0"/>
+        <v>-2880812</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="1"/>
-        <v>-995071.60691135703</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>-2381180</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>11</v>
       </c>
@@ -2785,10 +3304,10 @@
       <c r="E12">
         <v>13</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12">
         <v>14</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="14">
         <v>15</v>
       </c>
       <c r="H12">
@@ -2807,51 +3326,51 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="5">
         <f>$C$4/((1+$C$3)^C12)+L9</f>
-        <v>-707445.09719214321</v>
+        <v>-1881548</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" ref="D13:L13" si="2">$C$4/((1+$C$3)^D12)+C13</f>
-        <v>-445966.45199285785</v>
+        <f t="shared" ref="D13:L13" si="1">$C$4/((1+$C$3)^D12)+C13</f>
+        <v>-1381916</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="2"/>
-        <v>-208258.59272078029</v>
-      </c>
-      <c r="F13" s="13">
-        <f t="shared" si="2"/>
-        <v>7839.4611629265419</v>
-      </c>
-      <c r="G13" s="5">
-        <f t="shared" si="2"/>
-        <v>204292.23742084185</v>
+        <f t="shared" si="1"/>
+        <v>-882284</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" si="1"/>
+        <v>-382652</v>
+      </c>
+      <c r="G13" s="13">
+        <f t="shared" si="1"/>
+        <v>116980</v>
       </c>
       <c r="H13" s="5">
-        <f t="shared" si="2"/>
-        <v>382885.67038258305</v>
+        <f t="shared" si="1"/>
+        <v>616612</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="2"/>
-        <v>545243.33671143861</v>
+        <f t="shared" si="1"/>
+        <v>1116244</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="2"/>
-        <v>692841.21519221645</v>
+        <f t="shared" si="1"/>
+        <v>1615876</v>
       </c>
       <c r="K13" s="5">
-        <f t="shared" si="2"/>
-        <v>827021.10472019622</v>
+        <f t="shared" si="1"/>
+        <v>2115508</v>
       </c>
       <c r="L13" s="5">
-        <f t="shared" si="2"/>
-        <v>949002.82247290516</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>2615140</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
@@ -2863,7 +3382,7 @@
       <c r="K16" s="16"/>
       <c r="L16" s="16"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>0</v>
       </c>
@@ -2885,67 +3404,67 @@
       <c r="H17">
         <v>6</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="20">
         <v>7</v>
       </c>
       <c r="J17">
         <v>8</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="14">
         <v>9</v>
       </c>
       <c r="L17">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <f>-F3</f>
-        <v>-5250000</v>
+        <v>-5172500</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" ref="C18:L18" si="3">$C$4/((1+$C$3)^C17)+B18</f>
-        <v>-4503970.9090909092</v>
+        <f>$C$5/((1+$C$3)^C17)+B18</f>
+        <v>-4525868</v>
       </c>
       <c r="D18" s="5">
-        <f t="shared" si="3"/>
-        <v>-3825762.6446280992</v>
+        <f>$C$5/((1+$C$3)^D17)+C18</f>
+        <v>-3879236</v>
       </c>
       <c r="E18" s="5">
-        <f t="shared" si="3"/>
-        <v>-3209209.6769346357</v>
+        <f>$C$45/((1+$C$3)^E17)+D18</f>
+        <v>-3879236</v>
       </c>
       <c r="F18" s="5">
-        <f t="shared" si="3"/>
-        <v>-2648706.9790314874</v>
+        <f>$C$5/((1+$C$3)^F17)+E18</f>
+        <v>-3232604</v>
       </c>
       <c r="G18" s="5">
-        <f t="shared" si="3"/>
-        <v>-2139159.0718468069</v>
+        <f>$C$5/((1+$C$3)^G17)+F18</f>
+        <v>-2585972</v>
       </c>
       <c r="H18" s="5">
-        <f t="shared" si="3"/>
-        <v>-1675933.7016789156</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="3"/>
-        <v>-1254819.7287990146</v>
+        <f>$C$5/((1+$C$3)^H17)+G18</f>
+        <v>-1939340</v>
+      </c>
+      <c r="I18" s="21">
+        <f>$C$5/((1+$C$3)^I17)+H18</f>
+        <v>-1292708</v>
       </c>
       <c r="J18" s="5">
-        <f t="shared" si="3"/>
-        <v>-871988.84436274087</v>
-      </c>
-      <c r="K18" s="5">
-        <f t="shared" si="3"/>
-        <v>-523960.76760249207</v>
+        <f>$C$5/((1+$C$3)^J17)+I18</f>
+        <v>-646076</v>
+      </c>
+      <c r="K18" s="13">
+        <f>$C$5/((1+$C$3)^K17)+J18</f>
+        <v>556</v>
       </c>
       <c r="L18" s="5">
-        <f t="shared" si="3"/>
-        <v>-207571.60691135679</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="14">
+        <f>$C$5/((1+$C$3)^L17)+K18</f>
+        <v>647188</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C21">
         <v>11</v>
       </c>
       <c r="D21">
@@ -2976,51 +3495,51 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="13">
-        <f>$C$4/((1+$C$3)^C21)+L18</f>
-        <v>80054.902807857026</v>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C22" s="5">
+        <f>$C$5/((1+$C$3)^C21)+L18</f>
+        <v>1293820</v>
       </c>
       <c r="D22" s="5">
-        <f t="shared" ref="D22:L22" si="4">$C$4/((1+$C$3)^D21)+C22</f>
-        <v>341533.54800714238</v>
+        <f>$C$5/((1+$C$3)^D21)+C22</f>
+        <v>1940452</v>
       </c>
       <c r="E22" s="5">
-        <f t="shared" si="4"/>
-        <v>579241.40727921994</v>
+        <f>$C$5/((1+$C$3)^E21)+D22</f>
+        <v>2587084</v>
       </c>
       <c r="F22" s="5">
-        <f t="shared" si="4"/>
-        <v>795339.46116292675</v>
+        <f>$C$5/((1+$C$3)^F21)+E22</f>
+        <v>3233716</v>
       </c>
       <c r="G22" s="5">
-        <f t="shared" si="4"/>
-        <v>991792.23742084205</v>
+        <f>$C$5/((1+$C$3)^G21)+F22</f>
+        <v>3880348</v>
       </c>
       <c r="H22" s="5">
-        <f t="shared" si="4"/>
-        <v>1170385.6703825833</v>
+        <f>$C$5/((1+$C$3)^H21)+G22</f>
+        <v>4526980</v>
       </c>
       <c r="I22" s="5">
-        <f t="shared" si="4"/>
-        <v>1332743.3367114388</v>
+        <f>$C$5/((1+$C$3)^I21)+H22</f>
+        <v>5173612</v>
       </c>
       <c r="J22" s="5">
-        <f t="shared" si="4"/>
-        <v>1480341.2151922167</v>
+        <f>$C$5/((1+$C$3)^J21)+I22</f>
+        <v>5820244</v>
       </c>
       <c r="K22" s="5">
-        <f t="shared" si="4"/>
-        <v>1614521.1047201965</v>
+        <f>$C$5/((1+$C$3)^K21)+J22</f>
+        <v>6466876</v>
       </c>
       <c r="L22" s="5">
-        <f t="shared" si="4"/>
-        <v>1736502.8224729053</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+        <f>$C$5/((1+$C$3)^L21)+K22</f>
+        <v>7113508</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C26" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
@@ -3032,7 +3551,7 @@
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>0</v>
       </c>
@@ -3067,54 +3586,54 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="5">
         <f>-F4</f>
-        <v>-8557500</v>
+        <v>-8637500</v>
       </c>
       <c r="C28" s="5">
-        <f t="shared" ref="C28:L28" si="5">$C$4/((1+$C$3)^C27)+B28</f>
-        <v>-7811470.9090909092</v>
+        <f>$C$6/((1+$C$3)^C27)+B28</f>
+        <v>-7801868</v>
       </c>
       <c r="D28" s="5">
-        <f t="shared" si="5"/>
-        <v>-7133262.6446280992</v>
+        <f>$C$6/((1+$C$3)^D27)+C28</f>
+        <v>-6966236</v>
       </c>
       <c r="E28" s="5">
-        <f t="shared" si="5"/>
-        <v>-6516709.6769346362</v>
+        <f>$C$6/((1+$C$3)^E27)+D28</f>
+        <v>-6130604</v>
       </c>
       <c r="F28" s="5">
-        <f t="shared" si="5"/>
-        <v>-5956206.9790314874</v>
+        <f>$C$6/((1+$C$3)^F27)+E28</f>
+        <v>-5294972</v>
       </c>
       <c r="G28" s="5">
-        <f t="shared" si="5"/>
-        <v>-5446659.0718468074</v>
+        <f>$C$6/((1+$C$3)^G27)+F28</f>
+        <v>-4459340</v>
       </c>
       <c r="H28" s="5">
-        <f t="shared" si="5"/>
-        <v>-4983433.7016789159</v>
+        <f>$C$6/((1+$C$3)^H27)+G28</f>
+        <v>-3623708</v>
       </c>
       <c r="I28" s="5">
-        <f t="shared" si="5"/>
-        <v>-4562319.7287990153</v>
+        <f>$C$6/((1+$C$3)^I27)+H28</f>
+        <v>-2788076</v>
       </c>
       <c r="J28" s="5">
-        <f t="shared" si="5"/>
-        <v>-4179488.8443627413</v>
+        <f>$C$6/((1+$C$3)^J27)+I28</f>
+        <v>-1952444</v>
       </c>
       <c r="K28" s="5">
-        <f t="shared" si="5"/>
-        <v>-3831460.7676024926</v>
+        <f>$C$6/((1+$C$3)^K27)+J28</f>
+        <v>-1116812</v>
       </c>
       <c r="L28" s="5">
-        <f t="shared" si="5"/>
-        <v>-3515071.6069113575</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C31">
+        <f>$C$6/((1+$C$3)^L27)+K28</f>
+        <v>-281180</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C31" s="14">
         <v>11</v>
       </c>
       <c r="D31">
@@ -3145,46 +3664,46 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="5">
-        <f>$C$4/((1+$C$3)^C31)+L28</f>
-        <v>-3227445.0971921436</v>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C32" s="13">
+        <f>$C$6/((1+$C$3)^C31)+L28</f>
+        <v>554452</v>
       </c>
       <c r="D32" s="5">
-        <f t="shared" ref="D32:L32" si="6">$C$4/((1+$C$3)^D31)+C32</f>
-        <v>-2965966.4519928582</v>
+        <f>$C$6/((1+$C$3)^D31)+C32</f>
+        <v>1390084</v>
       </c>
       <c r="E32" s="5">
-        <f t="shared" si="6"/>
-        <v>-2728258.5927207805</v>
+        <f>$C$6/((1+$C$3)^E31)+D32</f>
+        <v>2225716</v>
       </c>
       <c r="F32" s="5">
-        <f t="shared" si="6"/>
-        <v>-2512160.5388370738</v>
+        <f>$C$6/((1+$C$3)^F31)+E32</f>
+        <v>3061348</v>
       </c>
       <c r="G32" s="5">
-        <f t="shared" si="6"/>
-        <v>-2315707.7625791584</v>
+        <f>$C$6/((1+$C$3)^G31)+F32</f>
+        <v>3896980</v>
       </c>
       <c r="H32" s="5">
-        <f t="shared" si="6"/>
-        <v>-2137114.3296174174</v>
+        <f>$C$6/((1+$C$3)^H31)+G32</f>
+        <v>4732612</v>
       </c>
       <c r="I32" s="5">
-        <f t="shared" si="6"/>
-        <v>-1974756.6632885619</v>
+        <f>$C$6/((1+$C$3)^I31)+H32</f>
+        <v>5568244</v>
       </c>
       <c r="J32" s="5">
-        <f t="shared" si="6"/>
-        <v>-1827158.784807784</v>
+        <f>$C$6/((1+$C$3)^J31)+I32</f>
+        <v>6403876</v>
       </c>
       <c r="K32" s="5">
-        <f t="shared" si="6"/>
-        <v>-1692978.8952798042</v>
+        <f>$C$6/((1+$C$3)^K31)+J32</f>
+        <v>7239508</v>
       </c>
       <c r="L32" s="5">
-        <f t="shared" si="6"/>
-        <v>-1570997.1775270954</v>
+        <f>$C$6/((1+$C$3)^L31)+K32</f>
+        <v>8075140</v>
       </c>
     </row>
   </sheetData>

--- a/02_Codigo/04_BattBankDesign/01_codes/02_Pnom025/CAPEX_OPEX_ROI_25.xlsx
+++ b/02_Codigo/04_BattBankDesign/01_codes/02_Pnom025/CAPEX_OPEX_ROI_25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell PC\Desktop\Tesis Magister\02_Codigo\04_BattBankDesign\01_codes\02_Pnom025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desar\Documents\Tesis Magister\Tesis_Msc_LSZ\02_Codigo\04_BattBankDesign\01_codes\02_Pnom025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D32AA41-D265-44C1-8249-82A8F66CE0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67233AF1-EA0F-4624-A7BE-B0978D9A25D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{32DAA168-B565-429F-AAFE-E289AA3DABBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Costs 25%" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="83">
   <si>
     <t>Lowest Cost ($/kWh)</t>
   </si>
@@ -242,9 +242,6 @@
   </si>
   <si>
     <t>20 años</t>
-  </si>
-  <si>
-    <t>|</t>
   </si>
   <si>
     <t>10 años</t>
@@ -300,8 +297,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_ &quot;$&quot;* #,##0.0_ ;_ &quot;$&quot;* \-#,##0.0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
@@ -365,42 +362,40 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="42" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda [0]" xfId="1" builtinId="7"/>
@@ -738,26 +733,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CC14D7A-AB81-456B-B0DB-733EF237E819}">
   <dimension ref="B3:H26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>7</v>
       </c>
@@ -774,7 +769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -796,7 +791,7 @@
         <v>5040000</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -818,7 +813,7 @@
         <v>2835000</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -840,17 +835,17 @@
         <v>6300000</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -870,7 +865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>4</v>
       </c>
@@ -892,17 +887,17 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="16" t="s">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
         <v>10</v>
       </c>
@@ -922,7 +917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -947,7 +942,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>14</v>
       </c>
@@ -972,18 +967,18 @@
         <v>370000</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="16" t="s">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B15" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
         <v>10</v>
       </c>
@@ -1003,7 +998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C17">
         <v>1</v>
       </c>
@@ -1025,17 +1020,17 @@
         <v>825000</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B18" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
         <v>10</v>
       </c>
@@ -1055,7 +1050,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -1080,17 +1075,17 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="16" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B21" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E22" t="s">
         <v>22</v>
       </c>
@@ -1104,7 +1099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E23" s="1">
         <v>100000</v>
       </c>
@@ -1120,17 +1115,17 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="16" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E25" t="s">
         <v>22</v>
       </c>
@@ -1144,7 +1139,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E26" s="1">
         <v>50000</v>
       </c>
@@ -1177,31 +1172,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29A8CAA-C5C8-4FF3-BA68-5F71D3D769DB}">
   <dimension ref="B3:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="E3" s="16" t="s">
+      <c r="C3" s="18"/>
+      <c r="E3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="H3" s="16" t="s">
+      <c r="F3" s="18"/>
+      <c r="H3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="16"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I3" s="18"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>25</v>
       </c>
@@ -1224,7 +1219,7 @@
         <v>6300000</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>26</v>
       </c>
@@ -1247,7 +1242,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>27</v>
       </c>
@@ -1270,7 +1265,7 @@
         <v>720000</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>15</v>
       </c>
@@ -1293,7 +1288,7 @@
         <v>825000</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -1316,7 +1311,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>28</v>
       </c>
@@ -1339,7 +1334,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>29</v>
       </c>
@@ -1362,7 +1357,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>61</v>
       </c>
@@ -1385,81 +1380,81 @@
         <v>8637500</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="18">
+        <v>69</v>
+      </c>
+      <c r="C12" s="16">
         <f>C11*0.035</f>
         <v>258212.50000000003</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="18">
+        <v>69</v>
+      </c>
+      <c r="F12" s="16">
         <f>F11*0.035</f>
         <v>181037.50000000003</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
-      </c>
-      <c r="I12" s="18">
+        <v>69</v>
+      </c>
+      <c r="I12" s="16">
         <f>I11*0.035</f>
         <v>302312.5</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C13" s="1">
         <f>C11*C17</f>
-        <v>0</v>
+        <v>737750</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>59</v>
       </c>
       <c r="F13" s="1">
         <f>F11*C17</f>
-        <v>0</v>
+        <v>517250</v>
       </c>
       <c r="H13" s="14" t="s">
         <v>59</v>
       </c>
       <c r="I13" s="1">
         <f>I11*C17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+        <v>863750</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="8">
         <f>C11-C13+C12</f>
-        <v>7635712.5</v>
+        <v>6897962.5</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F14" s="8">
         <f>F11-F13+F12</f>
-        <v>5353537.5</v>
+        <v>4836287.5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>60</v>
       </c>
       <c r="I14" s="8">
         <f>I11-I13+I12</f>
-        <v>8939812.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+        <v>8076062.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="14" t="s">
         <v>62</v>
       </c>
       <c r="C17" s="10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1475,214 +1470,214 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAAF4CD5-5B27-45B4-BE42-4FE58799A9A6}">
   <dimension ref="B2:L19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B2" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="E2" s="16" t="s">
+      <c r="C2" s="18"/>
+      <c r="E2" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="18"/>
+      <c r="H2" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="16"/>
-      <c r="H2" s="16" t="s">
+      <c r="I2" s="18"/>
+      <c r="K2" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="K2" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L2" s="18"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" s="6">
         <f>5366*365</f>
         <v>1958590</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F3" s="6">
         <f>1929*365</f>
         <v>704085</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I3" s="6">
         <f>1929*365</f>
         <v>704085</v>
       </c>
       <c r="K3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L3" s="6">
         <f>1929*365</f>
         <v>704085</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" s="6">
         <f>6385*365</f>
         <v>2330525</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4" s="6">
         <f>4030*365</f>
         <v>1470950</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I4" s="6">
         <f>4030*365</f>
         <v>1470950</v>
       </c>
       <c r="K4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L4" s="6">
         <f>4030*365</f>
         <v>1470950</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" s="6">
         <f>(C3+C4)/2</f>
         <v>2144557.5</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5">
         <f>(F3+F4)/2</f>
         <v>1087517.5</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I5">
         <f>(I3+I4)/2</f>
         <v>1087517.5</v>
       </c>
       <c r="K5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L5">
         <f>(L3+L4)/2</f>
         <v>1087517.5</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6">
         <f>14.3*365</f>
         <v>5219.5</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F6">
         <f>5.1*365</f>
         <v>1861.4999999999998</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I6">
         <f>5.1*365</f>
         <v>1861.4999999999998</v>
       </c>
       <c r="K6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L6">
         <f>5.1*365</f>
         <v>1861.4999999999998</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7">
         <f>17*365</f>
         <v>6205</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F7">
         <f>10.8*365</f>
         <v>3942.0000000000005</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I7">
         <f>10.8*365</f>
         <v>3942.0000000000005</v>
       </c>
       <c r="K7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L7">
         <f>10.8*365</f>
         <v>3942.0000000000005</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8">
         <f>(C6+C7)/2</f>
         <v>5712.25</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F8">
         <f>(F6+F7)/2</f>
         <v>2901.75</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I8">
         <f>(I6+I7)/2</f>
         <v>2901.75</v>
       </c>
       <c r="K8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L8">
         <f>(L6+L7)/2</f>
         <v>2901.75</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>31</v>
       </c>
@@ -1712,7 +1707,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
         <v>32</v>
       </c>
@@ -1742,7 +1737,7 @@
         <v>870014</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>33</v>
       </c>
@@ -1768,7 +1763,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>34</v>
       </c>
@@ -1794,7 +1789,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>35</v>
       </c>
@@ -1802,151 +1797,151 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F13" s="1">
         <f>'Costs 25%'!G5/15</f>
         <v>336000</v>
       </c>
       <c r="H13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I13" s="1">
         <f>'Costs 25%'!G6/15</f>
         <v>189000</v>
       </c>
       <c r="K13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C14" s="1">
-        <f>50*C8*0</f>
-        <v>0</v>
+        <f>50*C8</f>
+        <v>285612.5</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>58</v>
       </c>
       <c r="F14" s="1">
-        <f>50*F8*0</f>
-        <v>0</v>
+        <f>50*F8</f>
+        <v>145087.5</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>58</v>
       </c>
       <c r="I14" s="1">
-        <f>50*I8*0</f>
-        <v>0</v>
+        <f>50*I8</f>
+        <v>145087.5</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>58</v>
       </c>
       <c r="L14" s="1">
-        <f>50*L8*0</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+        <f>50*L8</f>
+        <v>145087.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="9">
         <f>SUM(C10:C14)</f>
-        <v>1755646</v>
+        <v>2041258.5</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F15" s="9">
         <f>SUM(F10:F14)</f>
-        <v>1256014</v>
+        <v>1401101.5</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I15" s="9">
         <f>SUM(I10:I14)</f>
-        <v>1109014</v>
+        <v>1254101.5</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="L15" s="9">
         <f>SUM(L10:L14)</f>
-        <v>920014</v>
-      </c>
-    </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+        <v>1065101.5</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.35">
       <c r="E17" t="s">
         <v>37</v>
       </c>
       <c r="F17" s="5">
         <f>C15</f>
-        <v>1755646</v>
+        <v>2041258.5</v>
       </c>
       <c r="H17" t="s">
         <v>37</v>
       </c>
       <c r="I17" s="5">
         <f>C15</f>
-        <v>1755646</v>
+        <v>2041258.5</v>
       </c>
       <c r="K17" t="s">
         <v>37</v>
       </c>
       <c r="L17" s="5">
         <f>C15</f>
-        <v>1755646</v>
-      </c>
-    </row>
-    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
+        <v>2041258.5</v>
+      </c>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.35">
       <c r="E18" t="s">
         <v>38</v>
       </c>
       <c r="F18" s="5">
         <f>F15</f>
-        <v>1256014</v>
+        <v>1401101.5</v>
       </c>
       <c r="H18" t="s">
         <v>38</v>
       </c>
       <c r="I18" s="5">
         <f>I15</f>
-        <v>1109014</v>
+        <v>1254101.5</v>
       </c>
       <c r="K18" t="s">
         <v>38</v>
       </c>
       <c r="L18" s="5">
         <f>L15</f>
-        <v>920014</v>
-      </c>
-    </row>
-    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
+        <v>1065101.5</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12" x14ac:dyDescent="0.35">
       <c r="E19" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F19" s="8">
         <f>F17-F18</f>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I19" s="8">
         <f>I17-I18</f>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>39</v>
       </c>
       <c r="L19" s="8">
         <f>L17-L18</f>
-        <v>835632</v>
+        <v>976157</v>
       </c>
     </row>
   </sheetData>
@@ -1962,30 +1957,32 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9148CD0-5187-4E9B-AB88-218957DBEFDE}">
-  <dimension ref="B1:P16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:O16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H1" s="16" t="s">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="H1" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="18"/>
+      <c r="K1" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="K1" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L1" s="16"/>
-      <c r="N1" s="16" t="s">
+      <c r="L1" s="18"/>
+      <c r="N1" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="O1" s="16"/>
-    </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O1" s="18"/>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>40</v>
       </c>
@@ -1997,31 +1994,31 @@
       </c>
       <c r="F2" s="5">
         <f>'CAPEX 25%'!C14</f>
-        <v>7635712.5</v>
+        <v>6897962.5</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>43</v>
       </c>
       <c r="I2" s="8">
         <f>SUM($C$9:$L$9)-F2</f>
-        <v>-4283141.1104840897</v>
+        <v>-2602456.9218978435</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>43</v>
       </c>
       <c r="L2" s="8">
         <f>SUM($C$9:$L$9)+SUM($C$14:$G$14)-F2</f>
-        <v>-3359123.0441939728</v>
+        <v>-1418552.3015731201</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>43</v>
       </c>
       <c r="O2" s="8">
         <f>SUM($C$9:$L$9)+SUM($C$14:$L$14)-F2</f>
-        <v>-2730251.8745212983</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+        <v>-612806.71008948795</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>41</v>
       </c>
@@ -2033,103 +2030,100 @@
       </c>
       <c r="F3" s="5">
         <f>'CAPEX 25%'!F14</f>
-        <v>5353537.5</v>
+        <v>4836287.5</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>47</v>
       </c>
       <c r="I3" s="8">
         <f>SUM($C$10:$L$10)-F3</f>
-        <v>-1014584.1448396975</v>
+        <v>445600.0437465487</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>47</v>
       </c>
       <c r="L3" s="8">
         <f>SUM($C$10:$L$10)+SUM($C$15:$G$15)-F3</f>
-        <v>181295.32293120399</v>
+        <v>1901366.0655520568</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>47</v>
       </c>
       <c r="O3" s="8">
         <f>SUM($C$10:$L$10)+SUM($C$15:$L$15)-F3</f>
-        <v>995190.79437374696</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+        <v>2892135.9588055573</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="5">
         <f>'OPEX 25%'!F19</f>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="E4" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="5">
         <f>'CAPEX 25%'!I14</f>
-        <v>8939812.5</v>
+        <v>8076062.5</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>48</v>
       </c>
       <c r="I4" s="8">
         <f>SUM($C$11:$L$11)-F4</f>
-        <v>-2766443.6718342882</v>
+        <v>-929144.73686537147</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>48</v>
       </c>
       <c r="L4" s="8">
         <f>SUM($C$11:$L$11)+SUM($C$16:$G$16)-F4</f>
-        <v>-1064972.274406109</v>
+        <v>1040651.0897284076</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>48</v>
       </c>
       <c r="O4" s="8">
         <f>SUM($C$11:$L$11)+SUM($C$16:$L$16)-F4</f>
-        <v>93020.568917047232</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+        <v>2381261.0308953468</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="5">
         <f>'OPEX 25%'!I19</f>
-        <v>646632</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+        <v>787157</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="5">
         <f>'OPEX 25%'!L15</f>
-        <v>920014</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C7" s="16" t="s">
+        <v>1065101.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C7" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="P7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C8" s="2">
         <v>1</v>
       </c>
@@ -2161,146 +2155,146 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="19" t="s">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B9" s="17" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="5">
         <f>$C$4/((1+$C$3)^C8)</f>
-        <v>462622.22222222219</v>
+        <v>592737.96296296292</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" ref="D9:L9" si="0">$C$4/((1+$C$3)^D8)</f>
-        <v>428353.90946502052</v>
+        <v>548831.4471879286</v>
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>396623.99024538934</v>
+        <v>508177.26591474871</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>367244.43541239755</v>
+        <v>470534.50547661912</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>340041.14390036807</v>
+        <v>435680.0976635362</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="0"/>
-        <v>314852.9110188593</v>
+        <v>403407.49783660757</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>291530.47316561046</v>
+        <v>373525.46095982182</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="0"/>
-        <v>269935.62330149114</v>
+        <v>345856.9082961313</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="0"/>
-        <v>249940.39194582513</v>
+        <v>320237.87805197341</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="0"/>
-        <v>231426.28883872696</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
+        <v>296516.55375182722</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="17" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="5">
         <f>$C$5/((1+$C$3)^C8)</f>
-        <v>598733.33333333326</v>
+        <v>728849.07407407404</v>
       </c>
       <c r="D10" s="5">
         <f>$C$5/((1+$C$3)^D8)</f>
-        <v>554382.7160493827</v>
+        <v>674860.25377229077</v>
       </c>
       <c r="E10" s="5">
-        <f t="shared" ref="D10:L10" si="1">$C$5/((1+$C$3)^E8)</f>
-        <v>513317.3296753543</v>
+        <f t="shared" ref="E10:L10" si="1">$C$5/((1+$C$3)^E8)</f>
+        <v>624870.60534471367</v>
       </c>
       <c r="F10" s="5">
         <f t="shared" si="1"/>
-        <v>475293.82377347618</v>
+        <v>578583.8938376978</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" si="1"/>
-        <v>440086.87386432977</v>
+        <v>535725.82762749796</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" si="1"/>
-        <v>407487.84617067565</v>
+        <v>496042.43298842391</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="1"/>
-        <v>377303.56126914412</v>
+        <v>459298.54906335549</v>
       </c>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>349355.1493232816</v>
+        <v>425276.43431792175</v>
       </c>
       <c r="K10" s="5">
         <f t="shared" si="1"/>
-        <v>323476.99011414958</v>
+        <v>393774.47622029786</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" si="1"/>
-        <v>299515.73158717557</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="19" t="s">
+        <v>364605.9965002758</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="17" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="5">
         <f>$C$6/((1+$C$3)^C8)</f>
-        <v>851864.81481481472</v>
+        <v>986205.09259259258</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" ref="D11:L11" si="2">$C$6/((1+$C$3)^D8)</f>
-        <v>788763.71742112481</v>
+        <v>913152.86351165967</v>
       </c>
       <c r="E11" s="5">
         <f t="shared" si="2"/>
-        <v>730336.77538993035</v>
+        <v>845511.91065894417</v>
       </c>
       <c r="F11" s="5">
         <f t="shared" si="2"/>
-        <v>676237.75499067619</v>
+        <v>782881.3987582816</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="2"/>
-        <v>626146.06943581125</v>
+        <v>724890.18403544591</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="2"/>
-        <v>579764.87910723255</v>
+        <v>671194.61484763504</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="2"/>
-        <v>536819.33250669681</v>
+        <v>621476.49522929161</v>
       </c>
       <c r="J11" s="5">
         <f t="shared" si="2"/>
-        <v>497054.93750620075</v>
+        <v>575441.19928638113</v>
       </c>
       <c r="K11" s="5">
         <f t="shared" si="2"/>
-        <v>460236.0532464821</v>
+        <v>532815.92526516772</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="2"/>
-        <v>426144.49374674272</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="19"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="19"/>
+        <v>493348.07894922933</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B12" s="17"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="17"/>
       <c r="C13" s="2">
         <v>11</v>
       </c>
@@ -2332,139 +2326,139 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="17" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="5">
         <f t="shared" ref="C14:L14" si="3">$C$4/((1+$C$3)^C13)</f>
-        <v>214283.60077659905</v>
+        <v>274552.36458502518</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="3"/>
-        <v>198410.7414598139</v>
+        <v>254215.15239354182</v>
       </c>
       <c r="E14" s="5">
         <f t="shared" si="3"/>
-        <v>183713.6494998277</v>
+        <v>235384.40036439057</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" si="3"/>
-        <v>170105.23101835896</v>
+        <v>217948.51885591718</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="3"/>
-        <v>157504.84353551752</v>
+        <v>201804.18412584922</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="3"/>
-        <v>145837.81808844217</v>
+        <v>186855.726042453</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="3"/>
-        <v>135035.01674855757</v>
+        <v>173014.56115041944</v>
       </c>
       <c r="J14" s="5">
         <f t="shared" si="3"/>
-        <v>125032.42291533106</v>
+        <v>160198.66773186982</v>
       </c>
       <c r="K14" s="5">
         <f t="shared" si="3"/>
-        <v>115770.76195863985</v>
+        <v>148332.09975173129</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>107195.14996170357</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="19" t="s">
+        <v>137344.53680715861</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="17" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="5">
         <f>$C$5/((1+$C$3)^C13)</f>
-        <v>277329.38109923661</v>
+        <v>337598.14490766276</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" ref="D15:L15" si="4">$C$5/((1+$C$3)^D13)</f>
-        <v>256786.46398077463</v>
+        <v>312590.87491450255</v>
       </c>
       <c r="E15" s="5">
         <f t="shared" si="4"/>
-        <v>237765.24442664318</v>
+        <v>289435.99529120605</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="4"/>
-        <v>220153.00409874364</v>
+        <v>267996.29193630186</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="4"/>
-        <v>203845.37416550337</v>
+        <v>248144.71475583504</v>
       </c>
       <c r="H15" s="5">
         <f>$C$5/((1+$C$3)^H13)</f>
-        <v>188745.71681991051</v>
+        <v>229763.62477392133</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="4"/>
-        <v>174764.55261102825</v>
+        <v>212744.09701289012</v>
       </c>
       <c r="J15" s="5">
         <f t="shared" si="4"/>
-        <v>161819.03019539651</v>
+        <v>196985.27501193527</v>
       </c>
       <c r="K15" s="5">
         <f t="shared" si="4"/>
-        <v>149832.43536610788</v>
+        <v>182393.77315919931</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="4"/>
-        <v>138733.73645009988</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
+        <v>168883.12329555492</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="17" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="5">
         <f>$C$6/((1+$C$3)^C13)</f>
-        <v>394578.23495068768</v>
+        <v>456803.776804842</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" ref="D16:L16" si="5">$C$6/((1+$C$3)^D13)</f>
-        <v>365350.21754693304</v>
+        <v>422966.46000448329</v>
       </c>
       <c r="E16" s="5">
         <f t="shared" si="5"/>
-        <v>338287.2384693824</v>
+        <v>391635.61111526226</v>
       </c>
       <c r="F16" s="5">
         <f t="shared" si="5"/>
-        <v>313228.92450868734</v>
+        <v>362625.56584746501</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="5"/>
-        <v>290026.78195248829</v>
+        <v>335764.41282172682</v>
       </c>
       <c r="H16" s="5">
         <f t="shared" si="5"/>
-        <v>268543.31662267435</v>
+        <v>310892.97483493225</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="5"/>
-        <v>248651.21909506884</v>
+        <v>287863.86558790022</v>
       </c>
       <c r="J16" s="5">
         <f t="shared" si="5"/>
-        <v>230232.61027321185</v>
+        <v>266540.61628509278</v>
       </c>
       <c r="K16" s="5">
         <f t="shared" si="5"/>
-        <v>213178.34284556651</v>
+        <v>246796.86693064144</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="5"/>
-        <v>197387.35448663568</v>
+        <v>228515.61752837172</v>
       </c>
     </row>
   </sheetData>
@@ -2482,131 +2476,131 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8641AB-FA05-4689-970F-41940E5E4D56}">
   <dimension ref="B1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="E1" s="17" t="s">
+    <row r="1" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="E1" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="19"/>
+      <c r="H1" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="H1" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="17"/>
-      <c r="K1" s="17" t="s">
+      <c r="I1" s="19"/>
+      <c r="K1" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="17"/>
-    </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="L1" s="19"/>
+    </row>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="5">
         <f>'OPEX 25%'!F19</f>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F2" s="11">
         <f>IRR(B9:L9)</f>
-        <v>-7.0513545927848531E-2</v>
+        <v>-1.3353217406831708E-2</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>49</v>
       </c>
       <c r="I2" s="11">
         <f>IRR(B9:Q9)</f>
-        <v>-2.3246625458969161E-3</v>
+        <v>4.4515285877237076E-2</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>49</v>
       </c>
       <c r="L2" s="11">
         <f>IRR(B9:V9)</f>
-        <v>2.7111577966266731E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+        <v>6.7825784116982701E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="5">
         <f>'OPEX 25%'!I19</f>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F3" s="11">
         <f>IRR(B14:L14)</f>
-        <v>3.5897502017308236E-2</v>
+        <v>0.10002173172701911</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I3" s="11">
         <f>IRR(B14:Q14)</f>
-        <v>8.5505172945715024E-2</v>
+        <v>0.13994056220419182</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="L3" s="11">
         <f>IRR(B14:V14)</f>
-        <v>0.10412762263493414</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+        <v>0.15338333113384484</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="5">
         <f>'OPEX 25%'!L19</f>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F4" s="11">
         <f>IRR(B19:L19)</f>
-        <v>-1.2087531518178762E-2</v>
+        <v>3.6036556216557436E-2</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="11">
         <f>IRR(B19:Q19)</f>
-        <v>4.5560717055539657E-2</v>
+        <v>8.5621855508887679E-2</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>54</v>
       </c>
       <c r="L4" s="11">
         <f>IRR(B19:V19)</f>
-        <v>6.8743520278883308E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="C7" s="16" t="s">
+        <v>0.1042319143780932</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="C7" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-    </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>0</v>
       </c>
@@ -2671,107 +2665,107 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <f>-'CAPEX 25%'!C14</f>
-        <v>-7635712.5</v>
+        <v>-6897962.5</v>
       </c>
       <c r="C9" s="5">
         <f>$C$2</f>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" ref="C9:V9" si="0">$C$2</f>
-        <v>499632</v>
+        <f t="shared" ref="D9:V9" si="0">$C$2</f>
+        <v>640157</v>
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="M9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="P9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>499632</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="C12" s="16" t="s">
+        <v>640157</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="C12" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>0</v>
       </c>
@@ -2836,107 +2830,107 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <f>-'CAPEX 25%'!F14</f>
-        <v>-5353537.5</v>
+        <v>-4836287.5</v>
       </c>
       <c r="C14" s="5">
         <f>$C$3</f>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" ref="D14:V14" si="1">$C$3</f>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="E14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="K14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="M14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="N14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="O14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="P14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="S14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="T14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
+        <v>787157</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="1"/>
-        <v>646632</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="C17" s="16" t="s">
+        <v>787157</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="C17" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-    </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>0</v>
       </c>
@@ -3001,90 +2995,90 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B19" s="5">
         <f>-'CAPEX 25%'!I14</f>
-        <v>-8939812.5</v>
+        <v>-8076062.5</v>
       </c>
       <c r="C19" s="5">
         <f>$C$4</f>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" ref="D19:V19" si="2">$C$4</f>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="E19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="F19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="H19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="J19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="K19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="M19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="N19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="P19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="R19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="S19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="T19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="2"/>
-        <v>835632</v>
+        <v>976157</v>
       </c>
     </row>
   </sheetData>
@@ -3103,18 +3097,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8AEBD9-4AB4-44E4-A602-35786004721C}">
   <dimension ref="B2:L32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>40</v>
       </c>
@@ -3133,10 +3127,10 @@
       </c>
       <c r="I2" s="12">
         <f>F2/$C$4</f>
-        <v>14.765867678611459</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+        <v>11.524516642011257</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>41</v>
       </c>
@@ -3155,16 +3149,16 @@
       </c>
       <c r="I3" s="12">
         <f>F3/$C$5</f>
-        <v>7.9991401600910566</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+        <v>6.5711160543576437</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="5">
         <f>'OPEX 25%'!F19</f>
-        <v>499632</v>
+        <v>640157</v>
       </c>
       <c r="E4" t="s">
         <v>65</v>
@@ -3178,42 +3172,42 @@
       </c>
       <c r="I4" s="12">
         <f>F4/$C$6</f>
-        <v>10.336487831964309</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+        <v>8.8484741696264031</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="5">
         <f>'OPEX 25%'!I19</f>
-        <v>646632</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+        <v>787157</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="5">
         <f>'OPEX 25%'!L19</f>
-        <v>835632</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="16" t="s">
+        <v>976157</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>0</v>
       </c>
@@ -3238,7 +3232,7 @@
       <c r="I8">
         <v>7</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8">
         <v>8</v>
       </c>
       <c r="K8">
@@ -3248,53 +3242,53 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <f>-F2</f>
         <v>-7377500</v>
       </c>
       <c r="C9" s="5">
         <f>$C$4/((1+$C$3)^C8)+B9</f>
-        <v>-6877868</v>
+        <v>-6737343</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" ref="C9:L9" si="0">$C$4/((1+$C$3)^D8)+C9</f>
-        <v>-6378236</v>
+        <f t="shared" ref="D9:L9" si="0">$C$4/((1+$C$3)^D8)+C9</f>
+        <v>-6097186</v>
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>-5878604</v>
+        <v>-5457029</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>-5378972</v>
+        <v>-4816872</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>-4879340</v>
+        <v>-4176715</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="0"/>
-        <v>-4379708</v>
+        <v>-3536558</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>-3880076</v>
-      </c>
-      <c r="J9" s="21">
+        <v>-2896401</v>
+      </c>
+      <c r="J9" s="5">
         <f t="shared" si="0"/>
-        <v>-3380444</v>
+        <v>-2256244</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="0"/>
-        <v>-2880812</v>
+        <v>-1616087</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="0"/>
-        <v>-2381180</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+        <v>-975930</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C12">
         <v>11</v>
       </c>
@@ -3326,63 +3320,63 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C13" s="5">
         <f>$C$4/((1+$C$3)^C12)+L9</f>
-        <v>-1881548</v>
+        <v>-335773</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" ref="D13:L13" si="1">$C$4/((1+$C$3)^D12)+C13</f>
-        <v>-1381916</v>
+        <v>304384</v>
       </c>
       <c r="E13" s="5">
         <f t="shared" si="1"/>
-        <v>-882284</v>
+        <v>944541</v>
       </c>
       <c r="F13" s="5">
         <f t="shared" si="1"/>
-        <v>-382652</v>
+        <v>1584698</v>
       </c>
       <c r="G13" s="13">
         <f t="shared" si="1"/>
-        <v>116980</v>
+        <v>2224855</v>
       </c>
       <c r="H13" s="5">
         <f t="shared" si="1"/>
-        <v>616612</v>
+        <v>2865012</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="1"/>
-        <v>1116244</v>
+        <v>3505169</v>
       </c>
       <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>1615876</v>
+        <v>4145326</v>
       </c>
       <c r="K13" s="5">
         <f t="shared" si="1"/>
-        <v>2115508</v>
+        <v>4785483</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="1"/>
-        <v>2615140</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="16" t="s">
+        <v>5425640</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C16" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>0</v>
       </c>
@@ -3404,7 +3398,7 @@
       <c r="H17">
         <v>6</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17">
         <v>7</v>
       </c>
       <c r="J17">
@@ -3417,53 +3411,53 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" s="5">
         <f>-F3</f>
         <v>-5172500</v>
       </c>
       <c r="C18" s="5">
         <f>$C$5/((1+$C$3)^C17)+B18</f>
-        <v>-4525868</v>
+        <v>-4385343</v>
       </c>
       <c r="D18" s="5">
         <f>$C$5/((1+$C$3)^D17)+C18</f>
-        <v>-3879236</v>
+        <v>-3598186</v>
       </c>
       <c r="E18" s="5">
         <f>$C$45/((1+$C$3)^E17)+D18</f>
-        <v>-3879236</v>
+        <v>-3598186</v>
       </c>
       <c r="F18" s="5">
-        <f>$C$5/((1+$C$3)^F17)+E18</f>
-        <v>-3232604</v>
+        <f t="shared" ref="F18:L18" si="2">$C$5/((1+$C$3)^F17)+E18</f>
+        <v>-2811029</v>
       </c>
       <c r="G18" s="5">
-        <f>$C$5/((1+$C$3)^G17)+F18</f>
-        <v>-2585972</v>
+        <f t="shared" si="2"/>
+        <v>-2023872</v>
       </c>
       <c r="H18" s="5">
-        <f>$C$5/((1+$C$3)^H17)+G18</f>
-        <v>-1939340</v>
-      </c>
-      <c r="I18" s="21">
-        <f>$C$5/((1+$C$3)^I17)+H18</f>
-        <v>-1292708</v>
+        <f t="shared" si="2"/>
+        <v>-1236715</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="2"/>
+        <v>-449558</v>
       </c>
       <c r="J18" s="5">
-        <f>$C$5/((1+$C$3)^J17)+I18</f>
-        <v>-646076</v>
+        <f t="shared" si="2"/>
+        <v>337599</v>
       </c>
       <c r="K18" s="13">
-        <f>$C$5/((1+$C$3)^K17)+J18</f>
-        <v>556</v>
+        <f t="shared" si="2"/>
+        <v>1124756</v>
       </c>
       <c r="L18" s="5">
-        <f>$C$5/((1+$C$3)^L17)+K18</f>
-        <v>647188</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>1911913</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C21">
         <v>11</v>
       </c>
@@ -3495,63 +3489,63 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C22" s="5">
         <f>$C$5/((1+$C$3)^C21)+L18</f>
-        <v>1293820</v>
+        <v>2699070</v>
       </c>
       <c r="D22" s="5">
-        <f>$C$5/((1+$C$3)^D21)+C22</f>
-        <v>1940452</v>
+        <f t="shared" ref="D22:L22" si="3">$C$5/((1+$C$3)^D21)+C22</f>
+        <v>3486227</v>
       </c>
       <c r="E22" s="5">
-        <f>$C$5/((1+$C$3)^E21)+D22</f>
-        <v>2587084</v>
+        <f t="shared" si="3"/>
+        <v>4273384</v>
       </c>
       <c r="F22" s="5">
-        <f>$C$5/((1+$C$3)^F21)+E22</f>
-        <v>3233716</v>
+        <f t="shared" si="3"/>
+        <v>5060541</v>
       </c>
       <c r="G22" s="5">
-        <f>$C$5/((1+$C$3)^G21)+F22</f>
-        <v>3880348</v>
+        <f t="shared" si="3"/>
+        <v>5847698</v>
       </c>
       <c r="H22" s="5">
-        <f>$C$5/((1+$C$3)^H21)+G22</f>
-        <v>4526980</v>
+        <f t="shared" si="3"/>
+        <v>6634855</v>
       </c>
       <c r="I22" s="5">
-        <f>$C$5/((1+$C$3)^I21)+H22</f>
-        <v>5173612</v>
+        <f t="shared" si="3"/>
+        <v>7422012</v>
       </c>
       <c r="J22" s="5">
-        <f>$C$5/((1+$C$3)^J21)+I22</f>
-        <v>5820244</v>
+        <f t="shared" si="3"/>
+        <v>8209169</v>
       </c>
       <c r="K22" s="5">
-        <f>$C$5/((1+$C$3)^K21)+J22</f>
-        <v>6466876</v>
+        <f t="shared" si="3"/>
+        <v>8996326</v>
       </c>
       <c r="L22" s="5">
-        <f>$C$5/((1+$C$3)^L21)+K22</f>
-        <v>7113508</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C26" s="16" t="s">
+        <f t="shared" si="3"/>
+        <v>9783483</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C26" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>0</v>
       </c>
@@ -3586,53 +3580,53 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" s="5">
         <f>-F4</f>
         <v>-8637500</v>
       </c>
       <c r="C28" s="5">
-        <f>$C$6/((1+$C$3)^C27)+B28</f>
-        <v>-7801868</v>
+        <f t="shared" ref="C28:L28" si="4">$C$6/((1+$C$3)^C27)+B28</f>
+        <v>-7661343</v>
       </c>
       <c r="D28" s="5">
-        <f>$C$6/((1+$C$3)^D27)+C28</f>
-        <v>-6966236</v>
+        <f t="shared" si="4"/>
+        <v>-6685186</v>
       </c>
       <c r="E28" s="5">
-        <f>$C$6/((1+$C$3)^E27)+D28</f>
-        <v>-6130604</v>
+        <f t="shared" si="4"/>
+        <v>-5709029</v>
       </c>
       <c r="F28" s="5">
-        <f>$C$6/((1+$C$3)^F27)+E28</f>
-        <v>-5294972</v>
+        <f t="shared" si="4"/>
+        <v>-4732872</v>
       </c>
       <c r="G28" s="5">
-        <f>$C$6/((1+$C$3)^G27)+F28</f>
-        <v>-4459340</v>
+        <f t="shared" si="4"/>
+        <v>-3756715</v>
       </c>
       <c r="H28" s="5">
-        <f>$C$6/((1+$C$3)^H27)+G28</f>
-        <v>-3623708</v>
+        <f t="shared" si="4"/>
+        <v>-2780558</v>
       </c>
       <c r="I28" s="5">
-        <f>$C$6/((1+$C$3)^I27)+H28</f>
-        <v>-2788076</v>
+        <f t="shared" si="4"/>
+        <v>-1804401</v>
       </c>
       <c r="J28" s="5">
-        <f>$C$6/((1+$C$3)^J27)+I28</f>
-        <v>-1952444</v>
+        <f t="shared" si="4"/>
+        <v>-828244</v>
       </c>
       <c r="K28" s="5">
-        <f>$C$6/((1+$C$3)^K27)+J28</f>
-        <v>-1116812</v>
+        <f t="shared" si="4"/>
+        <v>147913</v>
       </c>
       <c r="L28" s="5">
-        <f>$C$6/((1+$C$3)^L27)+K28</f>
-        <v>-281180</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>1124070</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C31" s="14">
         <v>11</v>
       </c>
@@ -3664,46 +3658,46 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C32" s="13">
         <f>$C$6/((1+$C$3)^C31)+L28</f>
-        <v>554452</v>
+        <v>2100227</v>
       </c>
       <c r="D32" s="5">
-        <f>$C$6/((1+$C$3)^D31)+C32</f>
-        <v>1390084</v>
+        <f t="shared" ref="D32:L32" si="5">$C$6/((1+$C$3)^D31)+C32</f>
+        <v>3076384</v>
       </c>
       <c r="E32" s="5">
-        <f>$C$6/((1+$C$3)^E31)+D32</f>
-        <v>2225716</v>
+        <f t="shared" si="5"/>
+        <v>4052541</v>
       </c>
       <c r="F32" s="5">
-        <f>$C$6/((1+$C$3)^F31)+E32</f>
-        <v>3061348</v>
+        <f t="shared" si="5"/>
+        <v>5028698</v>
       </c>
       <c r="G32" s="5">
-        <f>$C$6/((1+$C$3)^G31)+F32</f>
-        <v>3896980</v>
+        <f t="shared" si="5"/>
+        <v>6004855</v>
       </c>
       <c r="H32" s="5">
-        <f>$C$6/((1+$C$3)^H31)+G32</f>
-        <v>4732612</v>
+        <f t="shared" si="5"/>
+        <v>6981012</v>
       </c>
       <c r="I32" s="5">
-        <f>$C$6/((1+$C$3)^I31)+H32</f>
-        <v>5568244</v>
+        <f t="shared" si="5"/>
+        <v>7957169</v>
       </c>
       <c r="J32" s="5">
-        <f>$C$6/((1+$C$3)^J31)+I32</f>
-        <v>6403876</v>
+        <f t="shared" si="5"/>
+        <v>8933326</v>
       </c>
       <c r="K32" s="5">
-        <f>$C$6/((1+$C$3)^K31)+J32</f>
-        <v>7239508</v>
+        <f t="shared" si="5"/>
+        <v>9909483</v>
       </c>
       <c r="L32" s="5">
-        <f>$C$6/((1+$C$3)^L31)+K32</f>
-        <v>8075140</v>
+        <f t="shared" si="5"/>
+        <v>10885640</v>
       </c>
     </row>
   </sheetData>
